--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484219_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484219_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.214</v>
+        <v>6.3156</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9726</v>
+        <v>3.9925</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2414</v>
+        <v>2.3232</v>
       </c>
       <c r="G2" t="n">
         <v>2.5168</v>
@@ -610,13 +610,13 @@
         <v>2.5395</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6075</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.0569</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6843</v>
+        <v>0.766</v>
       </c>
       <c r="V2" t="n">
         <v>2.5037</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>M. BATALLER LOPEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7262</v>
+        <v>3.3803</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8082</v>
+        <v>1.4112</v>
       </c>
       <c r="F3" t="n">
-        <v>1.918</v>
+        <v>1.9691</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.7823</v>
+        <v>-0.2674</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.9274</v>
+        <v>1.0269</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1451</v>
+        <v>-1.2943</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0512</v>
+        <v>0.1016</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.3639</v>
+        <v>2.0696</v>
       </c>
       <c r="L3" t="n">
-        <v>2.4151</v>
+        <v>-1.968</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8336</v>
+        <v>-0.369</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5636</v>
+        <v>-1.0427</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.27</v>
+        <v>0.6737</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5627</v>
+        <v>1.9534</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5627</v>
+        <v>1.9534</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3249</v>
+        <v>0.6865</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2025</v>
+        <v>0.091</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1224</v>
+        <v>0.5955</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6209</v>
+        <v>1.0078</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5545</v>
+        <v>1.2186</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0664</v>
+        <v>-0.2108</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2863</v>
+        <v>3.129</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5647</v>
+        <v>4.3529</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2784</v>
+        <v>-1.2239</v>
       </c>
       <c r="G4" t="n">
         <v>1.4899</v>
@@ -766,13 +766,13 @@
         <v>1.7581</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6845</v>
+        <v>0.1582</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1127</v>
+        <v>0.6756</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5718</v>
+        <v>-0.5174</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2772</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6695</v>
+        <v>2.7054</v>
       </c>
       <c r="E5" t="n">
-        <v>0.287</v>
+        <v>1.0598</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3826</v>
+        <v>1.6456</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1572</v>
+        <v>-0.7823</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1325</v>
+        <v>-2.9274</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0247</v>
+        <v>2.1451</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4327</v>
+        <v>0.0512</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3517</v>
+        <v>-2.3639</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0809</v>
+        <v>2.4151</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7245</v>
+        <v>-0.8336</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2192</v>
+        <v>-0.5636</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9437</v>
+        <v>-0.27</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4692</v>
+        <v>1.3042</v>
       </c>
       <c r="T5" t="n">
-        <v>0.831</v>
+        <v>0.4541</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6382</v>
+        <v>0.85</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1522</v>
+        <v>0.6209</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1522</v>
+        <v>0.0664</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. BATALLER LOPEZ</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6434</v>
+        <v>1.0629</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1373</v>
+        <v>-0.3197</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5061</v>
+        <v>1.3826</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2674</v>
+        <v>1.1572</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0269</v>
+        <v>0.1325</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2943</v>
+        <v>1.0247</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1016</v>
+        <v>0.4327</v>
       </c>
       <c r="K6" t="n">
-        <v>2.0696</v>
+        <v>0.3517</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.968</v>
+        <v>0.0809</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.369</v>
+        <v>0.7245</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0427</v>
+        <v>-0.2192</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6737</v>
+        <v>0.9437</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9534</v>
+        <v>0.1953</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0504</v>
+        <v>0.8626</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1829</v>
+        <v>0.2244</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1325</v>
+        <v>0.6382</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0078</v>
+        <v>-1.1522</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2108</v>
+        <v>-1.1522</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6353</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>3.0719</v>
+        <v>1.6356</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4366</v>
+        <v>-1.6273</v>
       </c>
       <c r="G7" t="n">
         <v>0.07199999999999999</v>
@@ -1000,13 +1000,13 @@
         <v>1.5627</v>
       </c>
       <c r="S7" t="n">
-        <v>2.528</v>
+        <v>0.9011</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5232</v>
+        <v>1.0869</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0048</v>
+        <v>-0.1858</v>
       </c>
       <c r="V7" t="n">
         <v>-1.5507</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>D. YUSTE MALO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9058</v>
+        <v>-0.0004</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9169</v>
+        <v>-1.4384</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8227</v>
+        <v>1.438</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.4793</v>
+        <v>-0.9917</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.6266</v>
+        <v>0.6127</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1473</v>
+        <v>-1.6044</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6915</v>
+        <v>-0.228</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9747</v>
+        <v>1.1064</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2833</v>
+        <v>-1.3344</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7878</v>
+        <v>-0.7638</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6518</v>
+        <v>-0.4937</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.136</v>
+        <v>-0.27</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9534</v>
+        <v>1.3674</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4084</v>
+        <v>0.1472</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7513</v>
+        <v>-0.2337</v>
       </c>
       <c r="U8" t="n">
-        <v>1.6571</v>
+        <v>0.381</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.4533</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.4533</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. YUSTE MALO</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8195</v>
+        <v>-0.2284</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9034</v>
+        <v>-0.2287</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0839</v>
+        <v>0.0003</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9917</v>
+        <v>0.313</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6127</v>
+        <v>-1.9934</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.6044</v>
+        <v>2.3063</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.228</v>
+        <v>1.6214</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1064</v>
+        <v>-0.9555</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3344</v>
+        <v>2.577</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7638</v>
+        <v>-1.3085</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4937</v>
+        <v>-1.0379</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.27</v>
+        <v>-0.2706</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6718</v>
+        <v>-0.0688</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6987</v>
+        <v>0.1033</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0269</v>
+        <v>-0.1721</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4533</v>
+        <v>-0.2772</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4533</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8236</v>
+        <v>-0.257</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3609</v>
+        <v>-1.0992</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4627</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.313</v>
+        <v>-2.4793</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9934</v>
+        <v>-2.6266</v>
       </c>
       <c r="I10" t="n">
-        <v>2.3063</v>
+        <v>0.1473</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6214</v>
+        <v>-0.6915</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9555</v>
+        <v>-0.9747</v>
       </c>
       <c r="L10" t="n">
-        <v>2.577</v>
+        <v>0.2833</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3085</v>
+        <v>-1.7878</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0379</v>
+        <v>-1.6518</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2706</v>
+        <v>-0.136</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1953</v>
+        <v>0.9767</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7581</v>
+        <v>1.9534</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.664</v>
+        <v>1.2456</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0289</v>
+        <v>0.569</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6351</v>
+        <v>0.6766</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0961</v>
+        <v>-1.8666</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4165</v>
+        <v>-0.2142</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6796</v>
+        <v>-1.6524</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9775</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1772</v>
+        <v>0.0523</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0605</v>
+        <v>0.1417</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1167</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9414</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>13.3413</v>
+        <v>14.2492</v>
       </c>
       <c r="E12" t="n">
-        <v>8.244</v>
+        <v>9.151800000000001</v>
       </c>
       <c r="F12" t="n">
         <v>5.0974</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0506999999999993</v>
+        <v>0.05069999999999997</v>
       </c>
       <c r="H12" t="n">
         <v>-4.6701</v>
@@ -1366,7 +1366,7 @@
         <v>10.0867</v>
       </c>
       <c r="K12" t="n">
-        <v>4.011</v>
+        <v>4.010999999999999</v>
       </c>
       <c r="L12" t="n">
         <v>6.075799999999999</v>
@@ -1375,7 +1375,7 @@
         <v>-10.0362</v>
       </c>
       <c r="N12" t="n">
-        <v>-8.681200000000002</v>
+        <v>-8.6812</v>
       </c>
       <c r="O12" t="n">
         <v>-1.3551</v>
@@ -1390,10 +1390,10 @@
         <v>15.6274</v>
       </c>
       <c r="S12" t="n">
-        <v>5.090100000000001</v>
+        <v>5.9981</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1475</v>
+        <v>3.0554</v>
       </c>
       <c r="U12" t="n">
         <v>2.9426</v>
@@ -1405,7 +1405,7 @@
         <v>3.8234</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.436399999999999</v>
+        <v>-3.4364</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.036</v>
+        <v>2.4769</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8506</v>
+        <v>1.7495</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1854</v>
+        <v>0.7274</v>
       </c>
       <c r="G13" t="n">
         <v>2.7222</v>
@@ -1468,13 +1468,13 @@
         <v>0.586</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.7719</v>
+        <v>-1.331</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5969</v>
+        <v>-0.698</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.175</v>
+        <v>-0.633</v>
       </c>
       <c r="V13" t="n">
         <v>0.4996</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.291</v>
+        <v>1.4854</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1541</v>
+        <v>2.4575</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8632</v>
+        <v>-0.9721</v>
       </c>
       <c r="G14" t="n">
         <v>0.7914</v>
@@ -1546,13 +1546,13 @@
         <v>0.586</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0864</v>
+        <v>0.108</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4704</v>
+        <v>-0.1671</v>
       </c>
       <c r="U14" t="n">
-        <v>0.384</v>
+        <v>0.2751</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4943</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="E15" t="n">
         <v>3.0645</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5702</v>
+        <v>-2.434</v>
       </c>
       <c r="G15" t="n">
         <v>-0.6102</v>
@@ -1624,13 +1624,13 @@
         <v>0.7814</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2861</v>
+        <v>-0.15</v>
       </c>
       <c r="T15" t="n">
         <v>0.0689</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.355</v>
+        <v>-0.2188</v>
       </c>
       <c r="V15" t="n">
         <v>0.6093</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>B. MORALES CONILL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3646</v>
+        <v>0.4453</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0227</v>
+        <v>2.3517</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3873</v>
+        <v>-1.9064</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0653</v>
+        <v>3.0169</v>
       </c>
       <c r="H16" t="n">
-        <v>0.119</v>
+        <v>4.3254</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0537</v>
+        <v>-1.3085</v>
       </c>
       <c r="J16" t="n">
-        <v>0.09</v>
+        <v>3.7306</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1433</v>
+        <v>5.0384</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0533</v>
+        <v>-1.3077</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0247</v>
+        <v>-0.7137</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0243</v>
+        <v>-0.7129</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0004</v>
+        <v>-0.0008</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.7814</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2993</v>
+        <v>-1.1577</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1127</v>
+        <v>-0.4023</v>
       </c>
       <c r="U16" t="n">
-        <v>0.412</v>
+        <v>-0.7554</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6294999999999999</v>
+        <v>0.004</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8461</v>
+        <v>-0.3261</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4756</v>
+        <v>0.3301</v>
       </c>
       <c r="G17" t="n">
-        <v>3.0169</v>
+        <v>0.0653</v>
       </c>
       <c r="H17" t="n">
-        <v>4.3254</v>
+        <v>0.119</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3085</v>
+        <v>-0.0537</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7306</v>
+        <v>0.09</v>
       </c>
       <c r="K17" t="n">
-        <v>5.0384</v>
+        <v>0.1433</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3077</v>
+        <v>-0.0533</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7137</v>
+        <v>-0.0247</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7129</v>
+        <v>-0.0243</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0008</v>
+        <v>-0.0004</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.2325</v>
+        <v>-0.0613</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.416</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.3246</v>
+        <v>0.3548</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. LLORENS LLAURADO</t>
+          <t>P. MARTÍNEZ FERIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,40 +1813,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6792</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1768</v>
+        <v>-1.196</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4976</v>
+        <v>0.6673</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3936</v>
+        <v>0.2293</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2047</v>
+        <v>-0.0808</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1889</v>
+        <v>0.3101</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9782</v>
+        <v>0.1837</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.385</v>
+        <v>0.1433</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.0405</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5846</v>
+        <v>0.0456</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1804</v>
+        <v>-0.2241</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4043</v>
+        <v>0.2696</v>
       </c>
       <c r="P18" t="n">
         <v>-0.7814</v>
@@ -1858,19 +1858,19 @@
         <v>0.1953</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2185</v>
+        <v>0.0234</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5009</v>
+        <v>-0.403</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2824</v>
+        <v>0.4264</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>F. LLORENS LLAURADO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7854</v>
+        <v>-0.9734</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3982</v>
+        <v>-1.9857</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6128</v>
+        <v>1.0124</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2293</v>
+        <v>-0.3936</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0808</v>
+        <v>-0.2047</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3101</v>
+        <v>-0.1889</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1837</v>
+        <v>-0.9782</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1433</v>
+        <v>-0.385</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0405</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0456</v>
+        <v>0.5846</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2241</v>
+        <v>0.1804</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2696</v>
+        <v>0.4043</v>
       </c>
       <c r="P19" t="n">
         <v>-0.7814</v>
@@ -1936,19 +1936,19 @@
         <v>0.1953</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2333</v>
+        <v>-0.0757</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6052</v>
+        <v>-0.308</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3719</v>
+        <v>0.2324</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>M. FENÉS HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.377</v>
+        <v>-1.4731</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2042</v>
+        <v>-0.708</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8273</v>
+        <v>-0.7651</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1655</v>
+        <v>-0.1352</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1111</v>
+        <v>0.9437</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0545</v>
+        <v>-1.079</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6712</v>
+        <v>0.3492</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7522</v>
+        <v>1.0233</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0809</v>
+        <v>-0.6741</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4943</v>
+        <v>-0.4844</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3589</v>
+        <v>-0.0795</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1354</v>
+        <v>-0.4049</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1721</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0192</v>
+        <v>-0.5565</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1432</v>
+        <v>-0.0805</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.124</v>
+        <v>-0.476</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9414</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>A. SAMAKE EL ALAOUI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4108</v>
+        <v>-1.6852</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8091</v>
+        <v>0.7779</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6017</v>
+        <v>-2.4631</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1352</v>
+        <v>-0.2232</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9437</v>
+        <v>0.5188</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.079</v>
+        <v>-0.742</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3492</v>
+        <v>2.0942</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0233</v>
+        <v>1.352</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6741</v>
+        <v>0.7422</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4844</v>
+        <v>-2.3174</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0795</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4049</v>
+        <v>-1.4842</v>
       </c>
       <c r="P21" t="n">
         <v>-0.7814</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4942</v>
+        <v>-0.0165</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1816</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3126</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>U. FERNANDEZ RUIZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9576</v>
+        <v>-1.8516</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7779</v>
+        <v>-2.4065</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.7355</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2232</v>
+        <v>-1.1655</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5188</v>
+        <v>-1.1111</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.742</v>
+        <v>-0.0545</v>
       </c>
       <c r="J22" t="n">
-        <v>2.0942</v>
+        <v>-0.6712</v>
       </c>
       <c r="K22" t="n">
-        <v>1.352</v>
+        <v>-0.7522</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7422</v>
+        <v>0.0809</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.3174</v>
+        <v>-0.4943</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.3589</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4842</v>
+        <v>-0.1354</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7814</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2888</v>
+        <v>-0.4554</v>
       </c>
       <c r="T22" t="n">
-        <v>0.08260000000000001</v>
+        <v>-0.0591</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3715</v>
+        <v>-0.3963</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6642</v>
+        <v>0.9414</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5545</v>
+        <v>0.2772</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2186</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1868</v>
+        <v>-3.6603</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9007</v>
+        <v>-2.7996</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.286</v>
+        <v>-0.8607</v>
       </c>
       <c r="G23" t="n">
         <v>-1.25</v>
@@ -2248,13 +2248,13 @@
         <v>1.1721</v>
       </c>
       <c r="S23" t="n">
-        <v>0.653</v>
+        <v>0.1795</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6435999999999999</v>
+        <v>-0.5425</v>
       </c>
       <c r="U23" t="n">
-        <v>1.2966</v>
+        <v>0.722</v>
       </c>
       <c r="V23" t="n">
         <v>-0.8317</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.501</v>
+        <v>-6.863</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.2788</v>
+        <v>-6.0765</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2223</v>
+        <v>-0.7865</v>
       </c>
       <c r="G24" t="n">
         <v>-3.0979</v>
@@ -2326,13 +2326,13 @@
         <v>1.3674</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.887</v>
+        <v>-0.249</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.22</v>
+        <v>-0.0177</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.667</v>
+        <v>-0.2312</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-13.3414</v>
+        <v>-11.9932</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.097300000000001</v>
+        <v>-5.097299999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.2441</v>
+        <v>-6.895800000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-0.05050000000000043</v>
@@ -2389,7 +2389,7 @@
         <v>-10.0867</v>
       </c>
       <c r="N25" t="n">
-        <v>-4.0109</v>
+        <v>-4.010899999999999</v>
       </c>
       <c r="O25" t="n">
         <v>-6.0758</v>
@@ -2404,16 +2404,16 @@
         <v>7.813699999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.090200000000001</v>
+        <v>-3.7422</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.9426</v>
+        <v>-2.942699999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.1476</v>
+        <v>-0.7990999999999998</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.3869999999999998</v>
+        <v>-0.387</v>
       </c>
       <c r="W25" t="n">
         <v>3.4364</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484219_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484219_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.0664</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484219_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,11 +715,16 @@
       <c r="X3" t="n">
         <v>-0.2108</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484219_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.129</v>
+        <v>2.7054</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3529</v>
+        <v>1.0598</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2239</v>
+        <v>1.6456</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4899</v>
+        <v>-0.7823</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5054999999999999</v>
+        <v>-2.9274</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9955</v>
+        <v>2.1451</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6774</v>
+        <v>0.0512</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0066</v>
+        <v>-2.3639</v>
       </c>
       <c r="L4" t="n">
-        <v>2.6707</v>
+        <v>2.4151</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.1874</v>
+        <v>-0.8336</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5121</v>
+        <v>-0.5636</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6753</v>
+        <v>-0.27</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1582</v>
+        <v>1.3042</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6756</v>
+        <v>0.4541</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5174</v>
+        <v>0.85</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2772</v>
+        <v>0.6209</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2772</v>
+        <v>0.0664</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484219_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +819,72 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7054</v>
+        <v>2.522</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0598</v>
+        <v>3.7459</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6456</v>
+        <v>-1.2239</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7823</v>
+        <v>0.8829</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.9274</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1451</v>
+        <v>1.3885</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0512</v>
+        <v>3.0704</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.3639</v>
+        <v>1.0066</v>
       </c>
       <c r="L5" t="n">
-        <v>2.4151</v>
+        <v>2.0638</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8336</v>
+        <v>-2.1874</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5636</v>
+        <v>-1.5121</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.27</v>
+        <v>-0.6753</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3042</v>
+        <v>0.1582</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4541</v>
+        <v>0.6756</v>
       </c>
       <c r="U5" t="n">
-        <v>0.85</v>
+        <v>-0.5174</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6209</v>
+        <v>-0.2772</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0664</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484219_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -939,11 +964,16 @@
       <c r="X6" t="n">
         <v>-1.1522</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484219_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.607</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6356</v>
+        <v>0.607</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6273</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.607</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9089</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.837</v>
+        <v>0.607</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1896</v>
+        <v>0.607</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9468</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2428</v>
+        <v>0.607</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1176</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0379</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0797</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9011</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0869</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1858</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.5507</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484219_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. YUSTE MALO</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0004</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4384</v>
+        <v>1.6356</v>
       </c>
       <c r="F8" t="n">
-        <v>1.438</v>
+        <v>-1.6273</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9917</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6127</v>
+        <v>0.9089</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6044</v>
+        <v>-0.837</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.228</v>
+        <v>2.1896</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1064</v>
+        <v>1.9468</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3344</v>
+        <v>0.2428</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7638</v>
+        <v>-2.1176</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4937</v>
+        <v>-1.0379</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.27</v>
+        <v>-1.0797</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1472</v>
+        <v>0.9011</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2337</v>
+        <v>1.0869</v>
       </c>
       <c r="U8" t="n">
-        <v>0.381</v>
+        <v>-0.1858</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4533</v>
+        <v>-1.5507</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4533</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484219_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>D. YUSTE MALO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2284</v>
+        <v>-0.0004</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2287</v>
+        <v>-1.4384</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0003</v>
+        <v>1.438</v>
       </c>
       <c r="G9" t="n">
-        <v>0.313</v>
+        <v>-0.9917</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9934</v>
+        <v>0.6127</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3063</v>
+        <v>-1.6044</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6214</v>
+        <v>-0.228</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9555</v>
+        <v>1.1064</v>
       </c>
       <c r="L9" t="n">
-        <v>2.577</v>
+        <v>-1.3344</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3085</v>
+        <v>-0.7638</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0379</v>
+        <v>-0.4937</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2706</v>
+        <v>-0.27</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0688</v>
+        <v>0.1472</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1033</v>
+        <v>-0.2337</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1721</v>
+        <v>0.381</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2772</v>
+        <v>0.4533</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2772</v>
+        <v>0.4533</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484219_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.257</v>
+        <v>-0.2284</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0992</v>
+        <v>-0.2287</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.0003</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4793</v>
+        <v>0.313</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.6266</v>
+        <v>-1.9934</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1473</v>
+        <v>2.3063</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6915</v>
+        <v>1.6214</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9747</v>
+        <v>-0.9555</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2833</v>
+        <v>2.577</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7878</v>
+        <v>-1.3085</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6518</v>
+        <v>-1.0379</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.136</v>
+        <v>-0.2706</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9534</v>
+        <v>1.7581</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2456</v>
+        <v>-0.0688</v>
       </c>
       <c r="T10" t="n">
-        <v>0.569</v>
+        <v>0.1033</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6766</v>
+        <v>-0.1721</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484219_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. COSTA RABANEDA</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8666</v>
+        <v>-0.257</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2142</v>
+        <v>-1.0992</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6524</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9775</v>
+        <v>-2.4793</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.573</v>
+        <v>-2.6266</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4045</v>
+        <v>0.1473</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6332</v>
+        <v>-0.6915</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0409</v>
+        <v>-0.9747</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6741</v>
+        <v>0.2833</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3443</v>
+        <v>-1.7878</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.614</v>
+        <v>-1.6518</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2696</v>
+        <v>-0.136</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.9534</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0523</v>
+        <v>1.2456</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1417</v>
+        <v>0.569</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.08939999999999999</v>
+        <v>0.6766</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484219_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. COSTA RABANEDA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,151 +1400,157 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>14.2492</v>
+        <v>-1.8666</v>
       </c>
       <c r="E12" t="n">
-        <v>9.151800000000001</v>
+        <v>-0.2142</v>
       </c>
       <c r="F12" t="n">
-        <v>5.0974</v>
+        <v>-1.6524</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05069999999999997</v>
+        <v>-0.9775</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.6701</v>
+        <v>-0.573</v>
       </c>
       <c r="I12" t="n">
-        <v>4.7207</v>
+        <v>-0.4045</v>
       </c>
       <c r="J12" t="n">
-        <v>10.0867</v>
+        <v>-0.6332</v>
       </c>
       <c r="K12" t="n">
-        <v>4.010999999999999</v>
+        <v>0.0409</v>
       </c>
       <c r="L12" t="n">
-        <v>6.075799999999999</v>
+        <v>-0.6741</v>
       </c>
       <c r="M12" t="n">
-        <v>-10.0362</v>
+        <v>-0.3443</v>
       </c>
       <c r="N12" t="n">
-        <v>-8.6812</v>
+        <v>-0.614</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3551</v>
+        <v>0.2696</v>
       </c>
       <c r="P12" t="n">
-        <v>7.813600000000001</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-7.8136</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>15.6274</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>5.9981</v>
+        <v>0.0523</v>
       </c>
       <c r="T12" t="n">
-        <v>3.0554</v>
+        <v>0.1417</v>
       </c>
       <c r="U12" t="n">
-        <v>2.9426</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3870000000000002</v>
+        <v>-0.9414</v>
       </c>
       <c r="W12" t="n">
-        <v>3.8234</v>
+        <v>0.2772</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.4364</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484219_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. OBIOLS PUIG</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CB. CORNELLÀ</t>
+          <t>CB NAVÀS VISCOLA</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4769</v>
+        <v>14.2492</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7495</v>
+        <v>9.151800000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7274</v>
+        <v>5.0974</v>
       </c>
       <c r="G13" t="n">
-        <v>2.7222</v>
+        <v>0.05070000000000041</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1129</v>
+        <v>-4.6701</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3906</v>
+        <v>4.7207</v>
       </c>
       <c r="J13" t="n">
-        <v>1.9479</v>
+        <v>10.0867</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7424</v>
+        <v>4.011</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7945</v>
+        <v>6.075899999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7743</v>
+        <v>-10.0362</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3705</v>
+        <v>-8.6812</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4039</v>
+        <v>-1.3551</v>
       </c>
       <c r="P13" t="n">
-        <v>0.586</v>
+        <v>7.813600000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-7.8136</v>
       </c>
       <c r="R13" t="n">
-        <v>0.586</v>
+        <v>15.6274</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.331</v>
+        <v>5.9981</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.698</v>
+        <v>3.0554</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.633</v>
+        <v>2.9426</v>
       </c>
       <c r="V13" t="n">
-        <v>0.4996</v>
+        <v>0.3869999999999998</v>
       </c>
       <c r="W13" t="n">
-        <v>0.4996</v>
+        <v>3.8234</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
-      </c>
+        <v>-3.4364</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. VIEJO ANDREU</t>
+          <t>M. OBIOLS PUIG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,40 +1562,40 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4854</v>
+        <v>2.4769</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4575</v>
+        <v>1.7495</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9721</v>
+        <v>0.7274</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7914</v>
+        <v>2.7222</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.0967</v>
+        <v>3.1129</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8881</v>
+        <v>-0.3906</v>
       </c>
       <c r="J14" t="n">
-        <v>2.6246</v>
+        <v>1.9479</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6127</v>
+        <v>2.7424</v>
       </c>
       <c r="L14" t="n">
-        <v>3.2373</v>
+        <v>-0.7945</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.8332</v>
+        <v>0.7743</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.484</v>
+        <v>0.3705</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.3492</v>
+        <v>0.4039</v>
       </c>
       <c r="P14" t="n">
         <v>0.586</v>
@@ -1546,28 +1607,33 @@
         <v>0.586</v>
       </c>
       <c r="S14" t="n">
-        <v>0.108</v>
+        <v>-1.331</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1671</v>
+        <v>-0.698</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2751</v>
+        <v>-0.633</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.4996</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.4996</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484219_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>F. VIEJO ANDREU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6304999999999999</v>
+        <v>1.4854</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0645</v>
+        <v>2.4575</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.434</v>
+        <v>-0.9721</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6102</v>
+        <v>0.7914</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4827</v>
+        <v>-1.0967</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.093</v>
+        <v>1.8881</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1677</v>
+        <v>2.6246</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0463</v>
+        <v>-0.6127</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1214</v>
+        <v>3.2373</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7779</v>
+        <v>-1.8332</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5636</v>
+        <v>-0.484</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2144</v>
+        <v>-1.3492</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.15</v>
+        <v>0.108</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0689</v>
+        <v>-0.1671</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2188</v>
+        <v>0.2751</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484219_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4453</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3517</v>
+        <v>3.0645</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9064</v>
+        <v>-2.434</v>
       </c>
       <c r="G16" t="n">
-        <v>3.0169</v>
+        <v>-0.6102</v>
       </c>
       <c r="H16" t="n">
-        <v>4.3254</v>
+        <v>0.4827</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.3085</v>
+        <v>-1.093</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7306</v>
+        <v>1.1677</v>
       </c>
       <c r="K16" t="n">
-        <v>5.0384</v>
+        <v>1.0463</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.3077</v>
+        <v>0.1214</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7137</v>
+        <v>-1.7779</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7129</v>
+        <v>-0.5636</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0008</v>
+        <v>-1.2144</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0.7814</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1577</v>
+        <v>-0.15</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4023</v>
+        <v>0.0689</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7554</v>
+        <v>-0.2188</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2186</v>
+        <v>0.6093</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X16" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484219_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1811,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.004</v>
+        <v>0.607</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3261</v>
+        <v>0.607</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3301</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0653</v>
+        <v>0.607</v>
       </c>
       <c r="H17" t="n">
-        <v>0.119</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0537</v>
+        <v>0.607</v>
       </c>
       <c r="J17" t="n">
-        <v>0.09</v>
+        <v>0.607</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1433</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0533</v>
+        <v>0.607</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0247</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0243</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0004</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1780,13 +1856,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0613</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.416</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3548</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1796,12 +1872,17 @@
       </c>
       <c r="X17" t="n">
         <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484219_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>B. MORALES CONILL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5286999999999999</v>
+        <v>0.4453</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.196</v>
+        <v>2.3517</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6673</v>
+        <v>-1.9064</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2293</v>
+        <v>3.0169</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0808</v>
+        <v>4.3254</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3101</v>
+        <v>-1.3085</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1837</v>
+        <v>3.7306</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1433</v>
+        <v>5.0384</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0405</v>
+        <v>-1.3077</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0456</v>
+        <v>-0.7137</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2241</v>
+        <v>-0.7129</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2696</v>
+        <v>-0.0008</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7814</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0234</v>
+        <v>-1.1577</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.403</v>
+        <v>-0.4023</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4264</v>
+        <v>-0.7554</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484219_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. LLORENS LLAURADO</t>
+          <t>G. PÉREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9734</v>
+        <v>0.307</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9857</v>
+        <v>0.307</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0124</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3936</v>
+        <v>0.307</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2047</v>
+        <v>0.307</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1889</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9782</v>
+        <v>0.307</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.385</v>
+        <v>0.307</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5846</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1804</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4043</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0757</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.308</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2324</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484219_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +2060,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4731</v>
+        <v>0.004</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.708</v>
+        <v>-0.3261</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7651</v>
+        <v>0.3301</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1352</v>
+        <v>0.0653</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9437</v>
+        <v>0.119</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.079</v>
+        <v>-0.0537</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3492</v>
+        <v>0.09</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0233</v>
+        <v>0.1433</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6741</v>
+        <v>-0.0533</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4844</v>
+        <v>-0.0247</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0795</v>
+        <v>-0.0243</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4049</v>
+        <v>-0.0004</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5565</v>
+        <v>-0.0613</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0805</v>
+        <v>-0.416</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.476</v>
+        <v>0.3548</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2030,12 +2121,17 @@
       </c>
       <c r="X20" t="n">
         <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484219_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>P. MARTINEZ FERIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6852</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7779</v>
+        <v>-1.196</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4631</v>
+        <v>0.6673</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2232</v>
+        <v>0.2293</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5188</v>
+        <v>-0.0808</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.742</v>
+        <v>0.3101</v>
       </c>
       <c r="J21" t="n">
-        <v>2.0942</v>
+        <v>0.1837</v>
       </c>
       <c r="K21" t="n">
-        <v>1.352</v>
+        <v>0.1433</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7422</v>
+        <v>0.0405</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.3174</v>
+        <v>0.0456</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.2241</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4842</v>
+        <v>0.2696</v>
       </c>
       <c r="P21" t="n">
         <v>-0.7814</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0165</v>
+        <v>0.0234</v>
       </c>
       <c r="T21" t="n">
-        <v>0.08260000000000001</v>
+        <v>-0.403</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.09909999999999999</v>
+        <v>0.4264</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484219_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>F. LLORENS LLAURADO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8516</v>
+        <v>-0.9734</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4065</v>
+        <v>-1.9857</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5548999999999999</v>
+        <v>1.0124</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1655</v>
+        <v>-0.3936</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1111</v>
+        <v>-0.2047</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0545</v>
+        <v>-0.1889</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6712</v>
+        <v>-0.9782</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7522</v>
+        <v>-0.385</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0809</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4943</v>
+        <v>0.5846</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3589</v>
+        <v>0.1804</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1354</v>
+        <v>0.4043</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1721</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4554</v>
+        <v>-0.0757</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0591</v>
+        <v>-0.308</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3963</v>
+        <v>0.2324</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9414</v>
+        <v>0.2772</v>
       </c>
       <c r="W22" t="n">
         <v>0.2772</v>
       </c>
       <c r="X22" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484219_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>M. FENES HERNANDEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6603</v>
+        <v>-1.4731</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7996</v>
+        <v>-0.708</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8607</v>
+        <v>-0.7651</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.25</v>
+        <v>-0.1352</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6012</v>
+        <v>0.9437</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3512</v>
+        <v>-1.079</v>
       </c>
       <c r="J23" t="n">
-        <v>0.673</v>
+        <v>0.3492</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.1627</v>
+        <v>1.0233</v>
       </c>
       <c r="L23" t="n">
-        <v>1.8358</v>
+        <v>-0.6741</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.923</v>
+        <v>-0.4844</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4384</v>
+        <v>-0.0795</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.4846</v>
+        <v>-0.4049</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.7581</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1795</v>
+        <v>-0.5565</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5425</v>
+        <v>-0.0805</v>
       </c>
       <c r="U23" t="n">
-        <v>0.722</v>
+        <v>-0.476</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.8317</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.8317</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484219_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G. PÉREZ LAYUNTA</t>
+          <t>A. SAMAKE EL ALAOUI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.863</v>
+        <v>-1.6852</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.0765</v>
+        <v>0.7779</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7865</v>
+        <v>-2.4631</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.0979</v>
+        <v>-0.2232</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.738</v>
+        <v>0.5188</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.3598</v>
+        <v>-0.742</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.1752</v>
+        <v>2.0942</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1049</v>
+        <v>1.352</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.2801</v>
+        <v>0.7422</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.9226</v>
+        <v>-2.3174</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8429</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0797</v>
+        <v>-1.4842</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.5162</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.8836</v>
+        <v>-1.9534</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.249</v>
+        <v>-0.0165</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0177</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2312</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484219_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>U. FERNANDEZ RUIZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,318 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
+        <v>-1.8516</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-2.4065</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.5548999999999999</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.1655</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-1.1111</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.0545</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.6712</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.7522</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.0809</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.4943</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.3589</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.1354</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.4554</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.0591</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.3963</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.9414</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.6642</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484219_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>R. PEREZ GALINDO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-4.2673</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-3.4066</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.8607</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-1.857</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1.6012</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.2558</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-1.1627</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.2288</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1.923</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.4384</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-1.4846</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-1.7581</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.1795</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.5425</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.8317</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.8317</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484219_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>G. PEREZ LAYUNTA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-7.17</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-6.3835</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.7865</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-3.4049</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-1.045</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-2.3598</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-1.4822</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.2021</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-1.2801</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-1.9226</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.8429</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-1.0797</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-3.5162</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-4.8836</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.249</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.0177</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.2312</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484219_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
         <v>-11.9932</v>
       </c>
-      <c r="E25" t="n">
-        <v>-5.097299999999999</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-6.895800000000001</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-0.05050000000000043</v>
-      </c>
-      <c r="H25" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="I25" t="n">
+      <c r="E28" t="n">
+        <v>-5.0973</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-6.895799999999999</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.05050000000000088</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.669999999999998</v>
+      </c>
+      <c r="I28" t="n">
         <v>-4.7206</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J28" t="n">
         <v>10.0363</v>
       </c>
-      <c r="K25" t="n">
-        <v>8.6813</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="K28" t="n">
+        <v>8.681300000000002</v>
+      </c>
+      <c r="L28" t="n">
         <v>1.3552</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M28" t="n">
         <v>-10.0867</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N28" t="n">
         <v>-4.010899999999999</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O28" t="n">
         <v>-6.0758</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P28" t="n">
         <v>-7.8139</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q28" t="n">
         <v>-15.6273</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R28" t="n">
         <v>7.813699999999999</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S28" t="n">
         <v>-3.7422</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T28" t="n">
         <v>-2.942699999999999</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U28" t="n">
         <v>-0.7990999999999998</v>
       </c>
-      <c r="V25" t="n">
-        <v>-0.387</v>
-      </c>
-      <c r="W25" t="n">
+      <c r="V28" t="n">
+        <v>-0.3869999999999999</v>
+      </c>
+      <c r="W28" t="n">
         <v>3.4364</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X28" t="n">
         <v>-3.8233</v>
       </c>
+      <c r="Y28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
